--- a/doc/Progress.xlsx
+++ b/doc/Progress.xlsx
@@ -427,6 +427,9 @@
       <c r="B2" t="str">
         <v>O</v>
       </c>
+      <c r="C2" t="str">
+        <v>DONE</v>
+      </c>
       <c r="E2" t="str">
         <v>DONE</v>
       </c>
@@ -438,6 +441,9 @@
       <c r="B3" t="str">
         <v>O</v>
       </c>
+      <c r="C3" t="str">
+        <v>DONE</v>
+      </c>
       <c r="D3" t="str">
         <v>issue_sovel!B2</v>
       </c>
@@ -452,6 +458,9 @@
       <c r="B4" t="str">
         <v>O</v>
       </c>
+      <c r="C4" t="str">
+        <v>DONE</v>
+      </c>
       <c r="E4" t="str">
         <v>DONE</v>
       </c>
@@ -463,6 +472,9 @@
       <c r="B5" t="str">
         <v>O</v>
       </c>
+      <c r="C5" t="str">
+        <v>DONE</v>
+      </c>
       <c r="E5" t="str">
         <v>DONE</v>
       </c>
@@ -474,6 +486,9 @@
       <c r="B6" t="str">
         <v>O</v>
       </c>
+      <c r="C6" t="str">
+        <v>DONE</v>
+      </c>
       <c r="E6" t="str">
         <v>DONE</v>
       </c>
@@ -483,7 +498,10 @@
         <v>register</v>
       </c>
       <c r="B7" t="str">
-        <v>X</v>
+        <v>O</v>
+      </c>
+      <c r="C7" t="str">
+        <v>DONE</v>
       </c>
       <c r="E7" t="str">
         <v>22/3/2026</v>
@@ -494,7 +512,10 @@
         <v>dmem</v>
       </c>
       <c r="B8" t="str">
-        <v>X</v>
+        <v>O</v>
+      </c>
+      <c r="C8" t="str">
+        <v>DONE</v>
       </c>
       <c r="E8" t="str">
         <v>22/3/2027</v>
@@ -508,7 +529,10 @@
         <v>imem</v>
       </c>
       <c r="B9" t="str">
-        <v>X</v>
+        <v>O</v>
+      </c>
+      <c r="C9" t="str">
+        <v>DONE</v>
       </c>
       <c r="E9" t="str">
         <v>22/3/2028</v>
